--- a/diseases/d169/2010-2014.xlsx
+++ b/diseases/d169/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1217,6 +1232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1655,6 +1685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1803,6 +1838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1951,6 +1991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2096,6 +2141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2244,6 +2294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2392,6 +2447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2537,6 +2597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2685,6 +2750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2833,6 +2903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2978,6 +3053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3126,6 +3206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3274,6 +3359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3419,6 +3509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3567,6 +3662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3715,6 +3815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3860,6 +3965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4008,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4156,6 +4271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4301,6 +4421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4449,6 +4574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4597,6 +4727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4742,6 +4877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4890,6 +5030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5038,6 +5183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5183,6 +5333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5479,6 +5639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5624,6 +5789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5772,6 +5942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5920,6 +6095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6065,6 +6245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6361,6 +6551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6506,6 +6701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6654,6 +6854,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6802,6 +7007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6947,6 +7157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7095,6 +7310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7243,6 +7463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7388,6 +7613,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7536,6 +7766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7684,6 +7919,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7829,6 +8069,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7977,6 +8222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8125,6 +8375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8270,6 +8525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8418,6 +8678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8566,6 +8831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8711,6 +8981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8859,6 +9134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9004,6 +9284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9152,6 +9437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9300,6 +9590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9445,6 +9740,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9593,6 +9893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9741,6 +10046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9886,6 +10196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10034,6 +10349,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10182,6 +10502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10327,6 +10652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10475,6 +10805,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10623,6 +10958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10768,6 +11108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10916,6 +11261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11061,6 +11411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11209,6 +11564,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11357,6 +11717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11502,6 +11867,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11650,6 +12020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11798,6 +12173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11943,6 +12323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12091,6 +12476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12236,6 +12626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12384,6 +12779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12532,6 +12932,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12677,6 +13082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12825,6 +13235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12973,6 +13388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13118,6 +13538,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13266,6 +13691,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13414,6 +13844,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13559,6 +13994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13707,6 +14147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13855,6 +14300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14000,6 +14450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14148,6 +14603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14296,6 +14756,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14441,6 +14906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14589,6 +15059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14737,6 +15212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14882,6 +15362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15030,6 +15515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15178,6 +15668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15323,6 +15818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15471,6 +15971,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15619,6 +16124,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15764,6 +16274,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15912,6 +16427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16060,6 +16580,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16205,6 +16730,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16353,6 +16883,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16501,6 +17036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16646,6 +17186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16794,6 +17339,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16939,6 +17489,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17087,6 +17642,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17235,6 +17795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17380,6 +17945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17528,6 +18098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17676,6 +18251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17821,6 +18401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17969,6 +18554,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18117,6 +18707,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18262,6 +18857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18410,6 +19010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18558,6 +19163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18703,6 +19313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18851,6 +19466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18999,6 +19619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19144,6 +19769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19292,6 +19922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19440,6 +20075,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19585,6 +20225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19733,6 +20378,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19881,6 +20531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20026,6 +20681,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20174,6 +20834,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20319,6 +20984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20467,6 +21137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20612,6 +21287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20760,6 +21440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20908,6 +21593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21053,6 +21743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21201,6 +21896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21346,6 +22046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21494,6 +22199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21642,6 +22352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21787,6 +22502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21935,6 +22655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22083,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22228,6 +22958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22376,6 +23111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22524,6 +23264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22669,6 +23414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22817,6 +23567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22965,6 +23720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23110,6 +23870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23258,6 +24023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23403,6 +24173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23551,6 +24326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23699,6 +24479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23844,6 +24629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23992,6 +24782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24140,6 +24935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24285,6 +25085,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24433,6 +25238,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24581,6 +25391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24726,6 +25541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24874,6 +25694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25022,6 +25847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25167,6 +25997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25315,6 +26150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25463,6 +26303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25606,6 +26451,11 @@
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">

--- a/diseases/d169/2010-2014.xlsx
+++ b/diseases/d169/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0.00205046890891935</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1074,11 +1044,6 @@
       <c r="R4" t="n">
         <v>0.00861176274645304</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1091,22 +1056,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1227,11 +1182,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1244,22 +1194,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,11 +1317,6 @@
       <c r="R6" t="n">
         <v>0.006151406726758049</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1394,22 +1329,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,11 +1455,6 @@
       <c r="R7" t="n">
         <v>0.01408130007574331</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1547,22 +1467,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1680,11 +1590,6 @@
       <c r="R8" t="n">
         <v>0.0082018756356774</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1697,22 +1602,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1833,11 +1728,6 @@
       <c r="R9" t="n">
         <v>0.02583528823935912</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1850,22 +1740,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1986,11 +1866,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2003,22 +1878,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2136,11 +2001,6 @@
       <c r="R11" t="n">
         <v>0.00205046890891935</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2153,22 +2013,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2289,11 +2139,6 @@
       <c r="R12" t="n">
         <v>0.00430588137322652</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2306,22 +2151,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2442,11 +2277,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2459,22 +2289,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2592,11 +2412,6 @@
       <c r="R14" t="n">
         <v>0.00205046890891935</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2609,22 +2424,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2745,11 +2550,6 @@
       <c r="R15" t="n">
         <v>0.03875293235903868</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2762,22 +2562,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2898,11 +2688,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2915,22 +2700,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3048,11 +2823,6 @@
       <c r="R17" t="n">
         <v>0.00205046890891935</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3065,22 +2835,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3201,11 +2961,6 @@
       <c r="R18" t="n">
         <v>0.01291764411967956</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3218,22 +2973,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3354,11 +3099,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3371,22 +3111,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3504,11 +3234,6 @@
       <c r="R20" t="n">
         <v>0.0041009378178387</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3521,22 +3246,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3657,11 +3372,6 @@
       <c r="R21" t="n">
         <v>0.03444705098581216</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3674,22 +3384,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3810,11 +3510,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3827,22 +3522,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3960,11 +3645,6 @@
       <c r="R23" t="n">
         <v>0.006151406726758049</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3977,22 +3657,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4113,11 +3783,6 @@
       <c r="R24" t="n">
         <v>0.01722352549290608</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4130,22 +3795,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4266,11 +3921,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4283,22 +3933,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4416,11 +4056,6 @@
       <c r="R26" t="n">
         <v>0.006151406726758049</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4433,22 +4068,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4569,11 +4194,6 @@
       <c r="R27" t="n">
         <v>0.01722352549290608</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4586,22 +4206,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4722,11 +4332,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4739,22 +4344,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4872,11 +4467,6 @@
       <c r="R29" t="n">
         <v>0.01435328236243545</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4889,22 +4479,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5025,11 +4605,6 @@
       <c r="R30" t="n">
         <v>0.00861176274645304</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5042,22 +4617,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5178,11 +4743,6 @@
       <c r="R31" t="n">
         <v>0.01408130007574331</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5195,22 +4755,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5328,11 +4878,6 @@
       <c r="R32" t="n">
         <v>0.04716078490514505</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5345,22 +4890,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5481,11 +5016,6 @@
       <c r="R33" t="n">
         <v>0.00861176274645304</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5498,22 +5028,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5634,11 +5154,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5651,22 +5166,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5784,11 +5289,6 @@
       <c r="R35" t="n">
         <v>0.01025234454459675</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5801,22 +5301,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5937,11 +5427,6 @@
       <c r="R36" t="n">
         <v>0.00430588137322652</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5954,22 +5439,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6090,11 +5565,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6107,22 +5577,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6240,11 +5700,6 @@
       <c r="R38" t="n">
         <v>0.004071027750394744</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6257,22 +5712,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6393,11 +5838,6 @@
       <c r="R39" t="n">
         <v>0.01289043156799661</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6410,22 +5850,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6546,11 +5976,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6563,22 +5988,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6696,11 +6111,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6713,22 +6123,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6849,11 +6249,6 @@
       <c r="R42" t="n">
         <v>0.008593621045331071</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6866,22 +6261,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7002,11 +6387,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7019,22 +6399,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7152,11 +6522,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7169,22 +6534,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7305,11 +6660,6 @@
       <c r="R45" t="n">
         <v>0.004296810522665536</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7322,22 +6672,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7458,11 +6798,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7475,22 +6810,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7608,11 +6933,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7625,22 +6945,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7761,11 +7071,6 @@
       <c r="R48" t="n">
         <v>0.008593621045331071</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7778,22 +7083,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7914,11 +7209,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7931,22 +7221,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8064,11 +7344,6 @@
       <c r="R50" t="n">
         <v>0.002035513875197372</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8081,22 +7356,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8217,11 +7482,6 @@
       <c r="R51" t="n">
         <v>0.01718724209066214</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8234,22 +7494,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8370,11 +7620,6 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8387,22 +7632,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8520,11 +7755,6 @@
       <c r="R53" t="n">
         <v>0.002035513875197372</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8537,22 +7767,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8673,11 +7893,6 @@
       <c r="R54" t="n">
         <v>0.03007767365865875</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8690,22 +7905,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8826,11 +8031,6 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8843,22 +8043,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8976,11 +8166,6 @@
       <c r="R56" t="n">
         <v>0.004071027750394744</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8993,22 +8178,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9129,11 +8304,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9146,22 +8316,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9279,11 +8439,6 @@
       <c r="R58" t="n">
         <v>0.008142055500789488</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9296,22 +8451,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9432,11 +8577,6 @@
       <c r="R59" t="n">
         <v>0.004296810522665536</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9449,22 +8589,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9585,11 +8715,6 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9602,22 +8727,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9735,11 +8850,6 @@
       <c r="R61" t="n">
         <v>0.006106541625592117</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9752,22 +8862,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9888,11 +8988,6 @@
       <c r="R62" t="n">
         <v>0.01289043156799661</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9905,22 +9000,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10041,11 +9126,6 @@
       <c r="R63" t="n">
         <v>0.02799955956692802</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10058,22 +9138,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10191,11 +9261,6 @@
       <c r="R64" t="n">
         <v>0.01017756937598686</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10208,22 +9273,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10344,11 +9399,6 @@
       <c r="R65" t="n">
         <v>0.004296810522665536</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10361,22 +9411,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10497,11 +9537,6 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10514,22 +9549,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10647,11 +9672,6 @@
       <c r="R67" t="n">
         <v>0.008142055500789488</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10664,22 +9684,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10800,11 +9810,6 @@
       <c r="R68" t="n">
         <v>0.008593621045331071</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10817,22 +9822,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10953,11 +9948,6 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10970,22 +9960,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11103,11 +10083,6 @@
       <c r="R70" t="n">
         <v>0.002035513875197372</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11120,22 +10095,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11256,11 +10221,6 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11273,22 +10233,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11406,11 +10356,6 @@
       <c r="R72" t="n">
         <v>0.004032292249574414</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11423,22 +10368,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11559,11 +10494,6 @@
       <c r="R73" t="n">
         <v>0.008566792345793776</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11576,22 +10506,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11712,11 +10632,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11729,22 +10644,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11862,11 +10767,6 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11879,22 +10779,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12015,11 +10905,6 @@
       <c r="R76" t="n">
         <v>0.01285018851869066</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12032,22 +10917,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12168,11 +11043,6 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12185,22 +11055,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12318,11 +11178,6 @@
       <c r="R78" t="n">
         <v>0.002016146124787207</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12335,22 +11190,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12471,11 +11316,6 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12488,22 +11328,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12621,11 +11451,6 @@
       <c r="R80" t="n">
         <v>0.004032292249574414</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12638,22 +11463,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12774,11 +11589,6 @@
       <c r="R81" t="n">
         <v>0.02998377321027821</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12791,22 +11601,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12927,11 +11727,6 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12944,22 +11739,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13077,11 +11862,6 @@
       <c r="R83" t="n">
         <v>0.002016146124787207</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13094,22 +11874,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13230,11 +12000,6 @@
       <c r="R84" t="n">
         <v>0.01713358469158755</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13247,22 +12012,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13383,11 +12138,6 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13400,22 +12150,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13533,11 +12273,6 @@
       <c r="R86" t="n">
         <v>0.002016146124787207</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13550,22 +12285,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13686,11 +12411,6 @@
       <c r="R87" t="n">
         <v>0.02998377321027821</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13703,22 +12423,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13839,11 +12549,6 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13856,22 +12561,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13989,11 +12684,6 @@
       <c r="R89" t="n">
         <v>0.002016146124787207</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14006,22 +12696,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14142,11 +12822,6 @@
       <c r="R90" t="n">
         <v>0.004283396172896888</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14159,22 +12834,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14295,11 +12960,6 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14312,22 +12972,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14445,11 +13095,6 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14462,22 +13107,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14598,11 +13233,6 @@
       <c r="R93" t="n">
         <v>0.01285018851869066</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14615,22 +13245,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14751,11 +13371,6 @@
       <c r="R94" t="n">
         <v>0.01388684250834703</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14768,22 +13383,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14901,11 +13506,6 @@
       <c r="R95" t="n">
         <v>0.002016146124787207</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14918,22 +13518,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15054,11 +13644,6 @@
       <c r="R96" t="n">
         <v>0.01713358469158755</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15071,22 +13656,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15207,11 +13782,6 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15224,22 +13794,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15357,11 +13917,6 @@
       <c r="R98" t="n">
         <v>0.02419375349744648</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15374,22 +13929,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15510,11 +14055,6 @@
       <c r="R99" t="n">
         <v>0.01713358469158755</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15527,22 +14067,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15663,11 +14193,6 @@
       <c r="R100" t="n">
         <v>0.01388684250834703</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15680,22 +14205,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15813,11 +14328,6 @@
       <c r="R101" t="n">
         <v>0.03024219187180811</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15830,22 +14340,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15966,11 +14466,6 @@
       <c r="R102" t="n">
         <v>0.01285018851869066</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15983,22 +14478,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16119,11 +14604,6 @@
       <c r="R103" t="n">
         <v>0.01388684250834703</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16136,22 +14616,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16269,11 +14739,6 @@
       <c r="R104" t="n">
         <v>0.01008073062393603</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16286,22 +14751,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16422,11 +14877,6 @@
       <c r="R105" t="n">
         <v>0.004283396172896888</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16439,22 +14889,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16575,11 +15015,6 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16592,22 +15027,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16725,11 +15150,6 @@
       <c r="R107" t="n">
         <v>0.003994314931501143</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16742,22 +15162,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16878,11 +15288,6 @@
       <c r="R108" t="n">
         <v>0.00854084946306562</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16895,22 +15300,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17031,11 +15426,6 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17048,22 +15438,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17181,11 +15561,6 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17198,22 +15573,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17334,11 +15699,6 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17351,22 +15711,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17484,11 +15834,6 @@
       <c r="R112" t="n">
         <v>0.001997157465750572</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17501,22 +15846,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17637,11 +15972,6 @@
       <c r="R113" t="n">
         <v>0.00854084946306562</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17654,22 +15984,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17790,11 +16110,6 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17807,22 +16122,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17940,11 +16245,6 @@
       <c r="R115" t="n">
         <v>0.001997157465750572</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17957,22 +16257,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18093,11 +16383,6 @@
       <c r="R116" t="n">
         <v>0.00427042473153281</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18110,22 +16395,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18246,11 +16521,6 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18263,22 +16533,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18396,11 +16656,6 @@
       <c r="R118" t="n">
         <v>0.003994314931501143</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18413,22 +16668,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18549,11 +16794,6 @@
       <c r="R119" t="n">
         <v>0.02135212365766405</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18566,22 +16806,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18702,11 +16932,6 @@
       <c r="R120" t="n">
         <v>0.0137658849708886</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18719,22 +16944,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18852,11 +17067,6 @@
       <c r="R121" t="n">
         <v>0.001997157465750572</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18869,22 +17079,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19005,11 +17205,6 @@
       <c r="R122" t="n">
         <v>0.02135212365766405</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19022,22 +17217,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19158,11 +17343,6 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19175,22 +17355,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19308,11 +17478,6 @@
       <c r="R124" t="n">
         <v>0.001997157465750572</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19325,22 +17490,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19461,11 +17616,6 @@
       <c r="R125" t="n">
         <v>0.02135212365766405</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19478,22 +17628,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19614,11 +17754,6 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19631,22 +17766,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19764,11 +17889,6 @@
       <c r="R127" t="n">
         <v>0.001997157465750572</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19781,22 +17901,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19917,11 +18027,6 @@
       <c r="R128" t="n">
         <v>0.01281127419459843</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19934,22 +18039,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20070,11 +18165,6 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20087,22 +18177,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20220,11 +18300,6 @@
       <c r="R130" t="n">
         <v>0.001997157465750572</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20237,22 +18312,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20373,11 +18438,6 @@
       <c r="R131" t="n">
         <v>0.00427042473153281</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20390,22 +18450,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20526,11 +18576,6 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20543,22 +18588,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20676,11 +18711,6 @@
       <c r="R133" t="n">
         <v>0.005991472397251715</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20693,22 +18723,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20829,11 +18849,6 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20846,22 +18861,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -20979,11 +18984,6 @@
       <c r="R135" t="n">
         <v>0.007988629863002287</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20996,22 +18996,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21132,11 +19122,6 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21149,22 +19134,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21282,11 +19257,6 @@
       <c r="R137" t="n">
         <v>0.003994314931501143</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21299,22 +19269,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21435,11 +19395,6 @@
       <c r="R138" t="n">
         <v>0.02135212365766405</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21452,22 +19407,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21588,11 +19533,6 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21605,22 +19545,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21738,11 +19668,6 @@
       <c r="R140" t="n">
         <v>0.003957335530340491</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21755,22 +19680,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21891,11 +19806,6 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21908,22 +19818,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22041,11 +19941,6 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22058,22 +19953,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22194,11 +20079,6 @@
       <c r="R143" t="n">
         <v>0.00426024734868299</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22211,22 +20091,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22347,11 +20217,6 @@
       <c r="R144" t="n">
         <v>0.01366213445849208</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22364,22 +20229,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22497,11 +20352,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22514,22 +20364,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22650,11 +20490,6 @@
       <c r="R146" t="n">
         <v>0.00426024734868299</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22667,22 +20502,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22803,11 +20628,6 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22820,22 +20640,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -22953,11 +20763,6 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22970,22 +20775,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23106,11 +20901,6 @@
       <c r="R149" t="n">
         <v>0.008520494697365981</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23123,22 +20913,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23259,11 +21039,6 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23276,22 +21051,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23409,11 +21174,6 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23426,22 +21186,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23562,11 +21312,6 @@
       <c r="R152" t="n">
         <v>0.02556148409209794</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23579,22 +21324,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23715,11 +21450,6 @@
       <c r="R153" t="n">
         <v>0.01366213445849208</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23732,22 +21462,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -23865,11 +21585,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23882,22 +21597,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24018,11 +21723,6 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24035,22 +21735,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24168,11 +21858,6 @@
       <c r="R156" t="n">
         <v>0.001978667765170246</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24185,22 +21870,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24321,11 +21996,6 @@
       <c r="R157" t="n">
         <v>0.01278074204604897</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24338,22 +22008,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24474,11 +22134,6 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24491,22 +22146,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -24624,11 +22269,6 @@
       <c r="R159" t="n">
         <v>0.001978667765170246</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24641,22 +22281,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24777,11 +22407,6 @@
       <c r="R160" t="n">
         <v>0.01278074204604897</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24794,22 +22419,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -24930,11 +22545,6 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24947,22 +22557,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -25080,11 +22680,6 @@
       <c r="R162" t="n">
         <v>0.001978667765170246</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25097,22 +22692,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25233,11 +22818,6 @@
       <c r="R163" t="n">
         <v>0.008520494697365981</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25250,22 +22830,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25386,11 +22956,6 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25403,22 +22968,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25536,11 +23091,6 @@
       <c r="R165" t="n">
         <v>0.007914671060680983</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25553,22 +23103,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -25689,11 +23229,6 @@
       <c r="R166" t="n">
         <v>0.00426024734868299</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25706,22 +23241,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -25842,11 +23367,6 @@
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25859,22 +23379,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -25992,11 +23502,6 @@
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26009,22 +23514,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26145,11 +23640,6 @@
       <c r="R169" t="n">
         <v>0.008520494697365981</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26162,22 +23652,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26298,11 +23778,6 @@
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26315,22 +23790,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26448,11 +23913,6 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26465,22 +23925,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>

--- a/diseases/d169/2010-2014.xlsx
+++ b/diseases/d169/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0.00205046890891935</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1182,6 +1212,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1194,12 +1229,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1317,6 +1362,11 @@
       <c r="R6" t="n">
         <v>0.006151406726758049</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1329,12 +1379,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1455,6 +1515,11 @@
       <c r="R7" t="n">
         <v>0.01408130007574331</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1467,12 +1532,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1590,6 +1665,11 @@
       <c r="R8" t="n">
         <v>0.0082018756356774</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1602,12 +1682,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1866,6 +1956,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1878,12 +1973,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2001,6 +2106,11 @@
       <c r="R11" t="n">
         <v>0.00205046890891935</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2013,12 +2123,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2277,6 +2397,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2289,12 +2414,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2412,6 +2547,11 @@
       <c r="R14" t="n">
         <v>0.00205046890891935</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2424,12 +2564,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2688,6 +2838,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2700,12 +2855,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2823,6 +2988,11 @@
       <c r="R17" t="n">
         <v>0.00205046890891935</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2835,12 +3005,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3099,6 +3279,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3111,12 +3296,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3234,6 +3429,11 @@
       <c r="R20" t="n">
         <v>0.0041009378178387</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3246,12 +3446,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3510,6 +3720,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3522,12 +3737,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3645,6 +3870,11 @@
       <c r="R23" t="n">
         <v>0.006151406726758049</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3657,12 +3887,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3921,6 +4161,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3933,12 +4178,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4056,6 +4311,11 @@
       <c r="R26" t="n">
         <v>0.006151406726758049</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4068,12 +4328,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4332,6 +4602,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4344,12 +4619,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4467,6 +4752,11 @@
       <c r="R29" t="n">
         <v>0.01435328236243545</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4479,12 +4769,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4743,6 +5043,11 @@
       <c r="R31" t="n">
         <v>0.01408130007574331</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4755,12 +5060,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4878,6 +5193,11 @@
       <c r="R32" t="n">
         <v>0.04716078490514505</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4890,12 +5210,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5154,6 +5484,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5166,12 +5501,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5289,6 +5634,11 @@
       <c r="R35" t="n">
         <v>0.01025234454459675</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5301,12 +5651,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5565,6 +5925,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5577,12 +5942,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5700,6 +6075,11 @@
       <c r="R38" t="n">
         <v>0.004071027750394744</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5712,12 +6092,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5976,6 +6366,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5988,12 +6383,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6111,6 +6516,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6123,12 +6533,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6387,6 +6807,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6399,12 +6824,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6522,6 +6957,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6534,12 +6974,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6798,6 +7248,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6810,12 +7265,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -6933,6 +7398,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6945,12 +7415,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7209,6 +7689,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7221,12 +7706,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7344,6 +7839,11 @@
       <c r="R50" t="n">
         <v>0.002035513875197372</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7356,12 +7856,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7620,6 +8130,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7632,12 +8147,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7755,6 +8280,11 @@
       <c r="R53" t="n">
         <v>0.002035513875197372</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7767,12 +8297,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8031,6 +8571,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8043,12 +8588,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8166,6 +8721,11 @@
       <c r="R56" t="n">
         <v>0.004071027750394744</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8178,12 +8738,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8304,6 +8874,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8316,12 +8891,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8439,6 +9024,11 @@
       <c r="R58" t="n">
         <v>0.008142055500789488</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8451,12 +9041,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8715,6 +9315,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8727,12 +9332,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8850,6 +9465,11 @@
       <c r="R61" t="n">
         <v>0.006106541625592117</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8862,12 +9482,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9126,6 +9756,11 @@
       <c r="R63" t="n">
         <v>0.02799955956692802</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9138,12 +9773,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9261,6 +9906,11 @@
       <c r="R64" t="n">
         <v>0.01017756937598686</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9273,12 +9923,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9537,6 +10197,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9549,12 +10214,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9672,6 +10347,11 @@
       <c r="R67" t="n">
         <v>0.008142055500789488</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9684,12 +10364,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -9948,6 +10638,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9960,12 +10655,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10083,6 +10788,11 @@
       <c r="R70" t="n">
         <v>0.002035513875197372</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10095,12 +10805,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10221,6 +10941,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10233,12 +10958,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10356,6 +11091,11 @@
       <c r="R72" t="n">
         <v>0.004032292249574414</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10368,12 +11108,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10632,6 +11382,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10644,12 +11399,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10767,6 +11532,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10779,12 +11549,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11043,6 +11823,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11055,12 +11840,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11178,6 +11973,11 @@
       <c r="R78" t="n">
         <v>0.002016146124787207</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11190,12 +11990,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11316,6 +12126,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11328,12 +12143,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11451,6 +12276,11 @@
       <c r="R80" t="n">
         <v>0.004032292249574414</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11463,12 +12293,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11727,6 +12567,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11739,12 +12584,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -11862,6 +12717,11 @@
       <c r="R83" t="n">
         <v>0.002016146124787207</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11874,12 +12734,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12138,6 +13008,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12150,12 +13025,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12273,6 +13158,11 @@
       <c r="R86" t="n">
         <v>0.002016146124787207</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12285,12 +13175,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12549,6 +13449,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12561,12 +13466,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -12684,6 +13599,11 @@
       <c r="R89" t="n">
         <v>0.002016146124787207</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12696,12 +13616,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -12960,6 +13890,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12972,12 +13907,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13095,6 +14040,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13107,12 +14057,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13371,6 +14331,11 @@
       <c r="R94" t="n">
         <v>0.01388684250834703</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13383,12 +14348,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13506,6 +14481,11 @@
       <c r="R95" t="n">
         <v>0.002016146124787207</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13518,12 +14498,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13782,6 +14772,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13794,12 +14789,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -13917,6 +14922,11 @@
       <c r="R98" t="n">
         <v>0.02419375349744648</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13929,12 +14939,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14193,6 +15213,11 @@
       <c r="R100" t="n">
         <v>0.01388684250834703</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14205,12 +15230,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14328,6 +15363,11 @@
       <c r="R101" t="n">
         <v>0.03024219187180811</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14340,12 +15380,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14604,6 +15654,11 @@
       <c r="R103" t="n">
         <v>0.01388684250834703</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14616,12 +15671,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -14739,6 +15804,11 @@
       <c r="R104" t="n">
         <v>0.01008073062393603</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14751,12 +15821,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15015,6 +16095,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15027,12 +16112,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15150,6 +16245,11 @@
       <c r="R107" t="n">
         <v>0.003994314931501143</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15162,12 +16262,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15426,6 +16536,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15438,12 +16553,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15561,6 +16686,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15573,12 +16703,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -15699,6 +16839,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15711,12 +16856,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -15834,6 +16989,11 @@
       <c r="R112" t="n">
         <v>0.001997157465750572</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15846,12 +17006,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16110,6 +17280,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16122,12 +17297,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16245,6 +17430,11 @@
       <c r="R115" t="n">
         <v>0.001997157465750572</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16257,12 +17447,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16521,6 +17721,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16533,12 +17738,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -16656,6 +17871,11 @@
       <c r="R118" t="n">
         <v>0.003994314931501143</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16668,12 +17888,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -16932,6 +18162,11 @@
       <c r="R120" t="n">
         <v>0.0137658849708886</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16944,12 +18179,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17067,6 +18312,11 @@
       <c r="R121" t="n">
         <v>0.001997157465750572</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17079,12 +18329,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17343,6 +18603,11 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17355,12 +18620,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -17478,6 +18753,11 @@
       <c r="R124" t="n">
         <v>0.001997157465750572</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17490,12 +18770,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -17754,6 +19044,11 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17766,12 +19061,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -17889,6 +19194,11 @@
       <c r="R127" t="n">
         <v>0.001997157465750572</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17901,12 +19211,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18165,6 +19485,11 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18177,12 +19502,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18300,6 +19635,11 @@
       <c r="R130" t="n">
         <v>0.001997157465750572</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18312,12 +19652,22 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -18576,6 +19926,11 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18588,12 +19943,22 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -18711,6 +20076,11 @@
       <c r="R133" t="n">
         <v>0.005991472397251715</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18723,12 +20093,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -18849,6 +20229,11 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18861,12 +20246,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -18984,6 +20379,11 @@
       <c r="R135" t="n">
         <v>0.007988629863002287</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18996,12 +20396,22 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19122,6 +20532,11 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19134,12 +20549,22 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -19257,6 +20682,11 @@
       <c r="R137" t="n">
         <v>0.003994314931501143</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19269,12 +20699,22 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19533,6 +20973,11 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19545,12 +20990,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -19668,6 +21123,11 @@
       <c r="R140" t="n">
         <v>0.003957335530340491</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19680,12 +21140,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -19806,6 +21276,11 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19818,12 +21293,22 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -19941,6 +21426,11 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19953,12 +21443,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -20217,6 +21717,11 @@
       <c r="R144" t="n">
         <v>0.01366213445849208</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20229,12 +21734,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -20352,6 +21867,11 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20364,12 +21884,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -20628,6 +22158,11 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20640,12 +22175,22 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -20763,6 +22308,11 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20775,12 +22325,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21039,6 +22599,11 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21051,12 +22616,22 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -21174,6 +22749,11 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21186,12 +22766,22 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -21450,6 +23040,11 @@
       <c r="R153" t="n">
         <v>0.01366213445849208</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21462,12 +23057,22 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -21585,6 +23190,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21597,12 +23207,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -21723,6 +23343,11 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21735,12 +23360,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -21858,6 +23493,11 @@
       <c r="R156" t="n">
         <v>0.001978667765170246</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21870,12 +23510,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -22134,6 +23784,11 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22146,12 +23801,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22269,6 +23934,11 @@
       <c r="R159" t="n">
         <v>0.001978667765170246</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22281,12 +23951,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -22545,6 +24225,11 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22557,12 +24242,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -22680,6 +24375,11 @@
       <c r="R162" t="n">
         <v>0.001978667765170246</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22692,12 +24392,22 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -22956,6 +24666,11 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22968,12 +24683,22 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23091,6 +24816,11 @@
       <c r="R165" t="n">
         <v>0.007914671060680983</v>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23103,12 +24833,22 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -23367,6 +25107,11 @@
       <c r="R167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23379,12 +25124,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -23502,6 +25257,11 @@
       <c r="R168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23514,12 +25274,22 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -23778,6 +25548,11 @@
       <c r="R170" t="n">
         <v>0</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23790,12 +25565,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -23913,6 +25698,11 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23925,12 +25715,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
